--- a/artfynd/A 18634-2025 artfynd.xlsx
+++ b/artfynd/A 18634-2025 artfynd.xlsx
@@ -1054,7 +1054,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124123594</v>
+        <v>124123602</v>
       </c>
       <c r="B5" t="n">
         <v>79869</v>
@@ -1097,10 +1097,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514171</v>
+        <v>514264</v>
       </c>
       <c r="R5" t="n">
-        <v>6944779</v>
+        <v>6944666</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124123602</v>
+        <v>124123508</v>
       </c>
       <c r="B6" t="n">
-        <v>79869</v>
+        <v>79829</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,25 +1172,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514264</v>
+        <v>513943</v>
       </c>
       <c r="R6" t="n">
-        <v>6944666</v>
+        <v>6944755</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124123508</v>
+        <v>124123530</v>
       </c>
       <c r="B7" t="n">
-        <v>79829</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,25 +1278,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513943</v>
+        <v>513914</v>
       </c>
       <c r="R7" t="n">
-        <v>6944755</v>
+        <v>6944835</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124123530</v>
+        <v>124123594</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,21 +1388,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513914</v>
+        <v>514171</v>
       </c>
       <c r="R8" t="n">
-        <v>6944835</v>
+        <v>6944779</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 18634-2025 artfynd.xlsx
+++ b/artfynd/A 18634-2025 artfynd.xlsx
@@ -1160,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124123530</v>
+        <v>124123602</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513914</v>
+        <v>514264</v>
       </c>
       <c r="R6" t="n">
-        <v>6944835</v>
+        <v>6944666</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124123540</v>
+        <v>124123530</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,21 +1282,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514085</v>
+        <v>513914</v>
       </c>
       <c r="R7" t="n">
-        <v>6944814</v>
+        <v>6944835</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1478,7 +1478,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124123602</v>
+        <v>124123540</v>
       </c>
       <c r="B9" t="n">
         <v>79891</v>
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514264</v>
+        <v>514085</v>
       </c>
       <c r="R9" t="n">
-        <v>6944666</v>
+        <v>6944814</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 18634-2025 artfynd.xlsx
+++ b/artfynd/A 18634-2025 artfynd.xlsx
@@ -1266,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124123530</v>
+        <v>124123594</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,21 +1282,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513914</v>
+        <v>514171</v>
       </c>
       <c r="R7" t="n">
-        <v>6944835</v>
+        <v>6944779</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124123594</v>
+        <v>124123530</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,21 +1388,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514171</v>
+        <v>513914</v>
       </c>
       <c r="R8" t="n">
-        <v>6944779</v>
+        <v>6944835</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 18634-2025 artfynd.xlsx
+++ b/artfynd/A 18634-2025 artfynd.xlsx
@@ -1054,10 +1054,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124123508</v>
+        <v>124123540</v>
       </c>
       <c r="B5" t="n">
-        <v>79851</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,25 +1066,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1097,10 +1097,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513943</v>
+        <v>514085</v>
       </c>
       <c r="R5" t="n">
-        <v>6944755</v>
+        <v>6944814</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124123602</v>
+        <v>124123530</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514264</v>
+        <v>513914</v>
       </c>
       <c r="R6" t="n">
-        <v>6944666</v>
+        <v>6944835</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124123530</v>
+        <v>124123508</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>79851</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,25 +1384,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513914</v>
+        <v>513943</v>
       </c>
       <c r="R8" t="n">
-        <v>6944835</v>
+        <v>6944755</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1478,7 +1478,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124123540</v>
+        <v>124123602</v>
       </c>
       <c r="B9" t="n">
         <v>79891</v>
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514085</v>
+        <v>514264</v>
       </c>
       <c r="R9" t="n">
-        <v>6944814</v>
+        <v>6944666</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 18634-2025 artfynd.xlsx
+++ b/artfynd/A 18634-2025 artfynd.xlsx
@@ -1054,7 +1054,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124123540</v>
+        <v>124123602</v>
       </c>
       <c r="B5" t="n">
         <v>79891</v>
@@ -1097,10 +1097,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514085</v>
+        <v>514264</v>
       </c>
       <c r="R5" t="n">
-        <v>6944814</v>
+        <v>6944666</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1478,7 +1478,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124123602</v>
+        <v>124123540</v>
       </c>
       <c r="B9" t="n">
         <v>79891</v>
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514264</v>
+        <v>514085</v>
       </c>
       <c r="R9" t="n">
-        <v>6944666</v>
+        <v>6944814</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 18634-2025 artfynd.xlsx
+++ b/artfynd/A 18634-2025 artfynd.xlsx
@@ -1054,7 +1054,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124123602</v>
+        <v>124123594</v>
       </c>
       <c r="B5" t="n">
         <v>79891</v>
@@ -1097,10 +1097,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514264</v>
+        <v>514171</v>
       </c>
       <c r="R5" t="n">
-        <v>6944666</v>
+        <v>6944779</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124123530</v>
+        <v>124123540</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513914</v>
+        <v>514085</v>
       </c>
       <c r="R6" t="n">
-        <v>6944835</v>
+        <v>6944814</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1266,7 +1266,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124123594</v>
+        <v>124123602</v>
       </c>
       <c r="B7" t="n">
         <v>79891</v>
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514171</v>
+        <v>514264</v>
       </c>
       <c r="R7" t="n">
-        <v>6944779</v>
+        <v>6944666</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124123508</v>
+        <v>124123530</v>
       </c>
       <c r="B8" t="n">
-        <v>79851</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,25 +1384,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513943</v>
+        <v>513914</v>
       </c>
       <c r="R8" t="n">
-        <v>6944755</v>
+        <v>6944835</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124123540</v>
+        <v>124123508</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>79851</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,25 +1490,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514085</v>
+        <v>513943</v>
       </c>
       <c r="R9" t="n">
-        <v>6944814</v>
+        <v>6944755</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 18634-2025 artfynd.xlsx
+++ b/artfynd/A 18634-2025 artfynd.xlsx
@@ -1160,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124123540</v>
+        <v>124123508</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>79851</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,25 +1172,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514085</v>
+        <v>513943</v>
       </c>
       <c r="R6" t="n">
-        <v>6944814</v>
+        <v>6944755</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124123602</v>
+        <v>124123530</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,21 +1282,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514264</v>
+        <v>513914</v>
       </c>
       <c r="R7" t="n">
-        <v>6944666</v>
+        <v>6944835</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124123530</v>
+        <v>124123602</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,21 +1388,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513914</v>
+        <v>514264</v>
       </c>
       <c r="R8" t="n">
-        <v>6944835</v>
+        <v>6944666</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124123508</v>
+        <v>124123540</v>
       </c>
       <c r="B9" t="n">
-        <v>79851</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,25 +1490,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513943</v>
+        <v>514085</v>
       </c>
       <c r="R9" t="n">
-        <v>6944755</v>
+        <v>6944814</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 18634-2025 artfynd.xlsx
+++ b/artfynd/A 18634-2025 artfynd.xlsx
@@ -1160,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124123508</v>
+        <v>124123602</v>
       </c>
       <c r="B6" t="n">
-        <v>79851</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,25 +1172,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513943</v>
+        <v>514264</v>
       </c>
       <c r="R6" t="n">
-        <v>6944755</v>
+        <v>6944666</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124123530</v>
+        <v>124123508</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>79851</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,25 +1278,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513914</v>
+        <v>513943</v>
       </c>
       <c r="R7" t="n">
-        <v>6944835</v>
+        <v>6944755</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124123602</v>
+        <v>124123530</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,21 +1388,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514264</v>
+        <v>513914</v>
       </c>
       <c r="R8" t="n">
-        <v>6944666</v>
+        <v>6944835</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 18634-2025 artfynd.xlsx
+++ b/artfynd/A 18634-2025 artfynd.xlsx
@@ -1054,7 +1054,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124123594</v>
+        <v>124123602</v>
       </c>
       <c r="B5" t="n">
         <v>79891</v>
@@ -1097,10 +1097,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514171</v>
+        <v>514264</v>
       </c>
       <c r="R5" t="n">
-        <v>6944779</v>
+        <v>6944666</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124123602</v>
+        <v>124123594</v>
       </c>
       <c r="B6" t="n">
         <v>79891</v>
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514264</v>
+        <v>514171</v>
       </c>
       <c r="R6" t="n">
-        <v>6944666</v>
+        <v>6944779</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 18634-2025 artfynd.xlsx
+++ b/artfynd/A 18634-2025 artfynd.xlsx
@@ -1054,7 +1054,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124123602</v>
+        <v>124123540</v>
       </c>
       <c r="B5" t="n">
         <v>79891</v>
@@ -1097,10 +1097,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514264</v>
+        <v>514085</v>
       </c>
       <c r="R5" t="n">
-        <v>6944666</v>
+        <v>6944814</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124123594</v>
+        <v>124123530</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514171</v>
+        <v>513914</v>
       </c>
       <c r="R6" t="n">
-        <v>6944779</v>
+        <v>6944835</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124123530</v>
+        <v>124123602</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,21 +1388,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513914</v>
+        <v>514264</v>
       </c>
       <c r="R8" t="n">
-        <v>6944835</v>
+        <v>6944666</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1478,7 +1478,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124123540</v>
+        <v>124123594</v>
       </c>
       <c r="B9" t="n">
         <v>79891</v>
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514085</v>
+        <v>514171</v>
       </c>
       <c r="R9" t="n">
-        <v>6944814</v>
+        <v>6944779</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 18634-2025 artfynd.xlsx
+++ b/artfynd/A 18634-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80675790</v>
+        <v>124123489</v>
       </c>
       <c r="B2" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rasktjärnen, Jmt</t>
+          <t>Bodtjärn, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514209.1665717741</v>
+        <v>514094</v>
       </c>
       <c r="R2" t="n">
-        <v>6944677.816511042</v>
+        <v>6944657</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-07-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-07-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,35 +761,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Erik Söderhjelm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Erik Söderhjelm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80675791</v>
+        <v>124123530</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,38 +787,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>514260, Jmt</t>
+          <t>Bodtjärn, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514259.9456324762</v>
+        <v>513914</v>
       </c>
       <c r="R3" t="n">
-        <v>6944655.030881747</v>
+        <v>6944835</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,22 +844,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-07-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-07-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,82 +862,66 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Erik Söderhjelm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Erik Söderhjelm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96561778</v>
+        <v>124123519</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bodtjärnen /100 m S/, Jmt</t>
+          <t>Bodtjärn, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514265.3553822166</v>
+        <v>513870</v>
       </c>
       <c r="R4" t="n">
-        <v>6944682.659070552</v>
+        <v>6944774</v>
       </c>
       <c r="S4" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,34 +943,14 @@
           <t>Bräcke</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Z-Brä-1740</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>209 skott totalt på två dellokaler. Varav 1 med blomstängel på väg att utvecklas. Detaljer i privata fynduppgifter. Summerat till Floraväkteriet.</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,37 +959,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Erik Söderhjelm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars Grönvik</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>124123540</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124123530</v>
+        <v>124123594</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1203,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513914</v>
+        <v>514171</v>
       </c>
       <c r="R6" t="n">
-        <v>6944835</v>
+        <v>6944779</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1266,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124123508</v>
+        <v>124123602</v>
       </c>
       <c r="B7" t="n">
-        <v>79851</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1309,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513943</v>
+        <v>514264</v>
       </c>
       <c r="R7" t="n">
-        <v>6944755</v>
+        <v>6944666</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1372,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124123602</v>
+        <v>124123455</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,26 +1292,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1415,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514264</v>
+        <v>514092</v>
       </c>
       <c r="R8" t="n">
-        <v>6944666</v>
+        <v>6944610</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,13 +1358,17 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack i tall</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1478,53 +1387,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124123594</v>
+        <v>80675791</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bodtjärn, Jmt</t>
+          <t>514260, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514171</v>
+        <v>514260</v>
       </c>
       <c r="R9" t="n">
-        <v>6944779</v>
+        <v>6944655</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,12 +1456,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2019-07-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2019-07-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,18 +1474,572 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Sven Bengtsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sven Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>94564975</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bodtjärn, dellokal 1, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>514269</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6944706</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-06-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-06-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Inga stänglar.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lars Grönvik</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lars Grönvik</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>94565032</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bodtjärn, dellokal 2, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>514267</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6944688</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-06-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-06-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>En stängel på väg att utvecklas.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lars Grönvik</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lars Grönvik</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>96561217</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bodtjärnen /100 m S/, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>514265</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6944683</v>
+      </c>
+      <c r="S12" t="n">
+        <v>75</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Z-Brä-1740</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2019-07-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2019-07-14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Noterad på lokal Störrestjärnen vid koordinat O1472960 N6946885 (±10m) RT90 2.5 gon. Kopia till Floraväkteriet.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Sven Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>80675790</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Rasktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>514209</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6944678</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2019-07-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2019-07-14</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sven Bengtsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sven Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>124123508</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bodtjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>513943</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6944755</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
           <t>Erik Söderhjelm</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>Erik Söderhjelm</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18634-2025 artfynd.xlsx
+++ b/artfynd/A 18634-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124123489</v>
+        <v>135538848</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>97461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrådmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cephalozia macounii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Austin) Austin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bodtjärn, Jmt</t>
+          <t>Barrskogen NV om Fisketjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514094</v>
+        <v>513946</v>
       </c>
       <c r="R2" t="n">
-        <v>6944657</v>
+        <v>6944708</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,22 +771,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erik Söderhjelm</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Söderhjelm</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124123530</v>
+        <v>135538849</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,37 +794,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bodtjärn, Jmt</t>
+          <t>Barrskogen NV om Fisketjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513914</v>
+        <v>513946</v>
       </c>
       <c r="R3" t="n">
-        <v>6944835</v>
+        <v>6944708</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -844,19 +848,29 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
@@ -865,22 +879,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erik Söderhjelm</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erik Söderhjelm</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124123519</v>
+        <v>124123489</v>
       </c>
       <c r="B4" t="n">
-        <v>80432</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +902,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -915,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513870</v>
+        <v>514094</v>
       </c>
       <c r="R4" t="n">
-        <v>6944774</v>
+        <v>6944657</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,32 +992,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124123540</v>
+        <v>124123530</v>
       </c>
       <c r="B5" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514085</v>
+        <v>513914</v>
       </c>
       <c r="R5" t="n">
-        <v>6944814</v>
+        <v>6944835</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124123594</v>
+        <v>124123519</v>
       </c>
       <c r="B6" t="n">
         <v>80432</v>
@@ -1117,10 +1131,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514171</v>
+        <v>513870</v>
       </c>
       <c r="R6" t="n">
-        <v>6944779</v>
+        <v>6944774</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,7 +1194,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124123602</v>
+        <v>124123540</v>
       </c>
       <c r="B7" t="n">
         <v>80432</v>
@@ -1218,10 +1232,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514264</v>
+        <v>514085</v>
       </c>
       <c r="R7" t="n">
-        <v>6944666</v>
+        <v>6944814</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124123455</v>
+        <v>124123594</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,27 +1306,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1320,10 +1333,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514092</v>
+        <v>514171</v>
       </c>
       <c r="R8" t="n">
-        <v>6944610</v>
+        <v>6944779</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1358,17 +1371,13 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack i tall</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1387,49 +1396,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>80675791</v>
+        <v>124123602</v>
       </c>
       <c r="B9" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>514260, Jmt</t>
+          <t>Bodtjärn, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514260</v>
+        <v>514264</v>
       </c>
       <c r="R9" t="n">
-        <v>6944655</v>
+        <v>6944666</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,12 +1464,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2019-07-14</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2019-07-14</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1474,77 +1482,64 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Erik Söderhjelm</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Erik Söderhjelm</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>94564975</v>
+        <v>124123455</v>
       </c>
       <c r="B10" t="n">
-        <v>99118</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bodtjärn, dellokal 1, Jmt</t>
+          <t>Bodtjärn, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514269</v>
+        <v>514092</v>
       </c>
       <c r="R10" t="n">
-        <v>6944706</v>
+        <v>6944610</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1571,17 +1566,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Inga stänglar.</t>
+          <t>Ringhack i tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1590,26 +1585,25 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lars Grönvik</t>
+          <t>Erik Söderhjelm</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars Grönvik</t>
+          <t>Erik Söderhjelm</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>94565032</v>
+        <v>80675791</v>
       </c>
       <c r="B11" t="n">
         <v>99118</v>
@@ -1637,29 +1631,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bodtjärn, dellokal 2, Jmt</t>
+          <t>514260, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514267</v>
+        <v>514260</v>
       </c>
       <c r="R11" t="n">
-        <v>6944688</v>
+        <v>6944655</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1686,17 +1672,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
+          <t>2019-07-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>En stängel på väg att utvecklas.</t>
+          <t>2019-07-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1709,22 +1690,27 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars Grönvik</t>
+          <t>Sven Bengtsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars Grönvik</t>
+          <t>Sven Bengtsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96561217</v>
+        <v>94564975</v>
       </c>
       <c r="B12" t="n">
         <v>99118</v>
@@ -1752,20 +1738,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bodtjärnen /100 m S/, Jmt</t>
+          <t>Bodtjärn, dellokal 1, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514265</v>
+        <v>514269</v>
       </c>
       <c r="R12" t="n">
-        <v>6944683</v>
+        <v>6944706</v>
       </c>
       <c r="S12" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1787,24 +1785,19 @@
           <t>Bräcke</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>Z-Brä-1740</t>
-        </is>
-      </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2019-07-14</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2019-07-14</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Noterad på lokal Störrestjärnen vid koordinat O1472960 N6946885 (±10m) RT90 2.5 gon. Kopia till Floraväkteriet.</t>
+          <t>Inga stänglar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1813,71 +1806,76 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Lars Grönvik</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Lars Grönvik</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>80675790</v>
+        <v>94565032</v>
       </c>
       <c r="B13" t="n">
-        <v>97989</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rasktjärnen, Jmt</t>
+          <t>Bodtjärn, dellokal 2, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514209</v>
+        <v>514267</v>
       </c>
       <c r="R13" t="n">
-        <v>6944678</v>
+        <v>6944688</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,12 +1902,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2019-07-14</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2019-07-14</t>
+          <t>2021-06-29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>En stängel på väg att utvecklas.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1922,71 +1925,63 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Lars Grönvik</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Lars Grönvik</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124123508</v>
+        <v>96561217</v>
       </c>
       <c r="B14" t="n">
-        <v>80392</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bodtjärn, Jmt</t>
+          <t>Bodtjärnen /100 m S/, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513943</v>
+        <v>514265</v>
       </c>
       <c r="R14" t="n">
-        <v>6944755</v>
+        <v>6944683</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2008,14 +2003,24 @@
           <t>Bräcke</t>
         </is>
       </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Z-Brä-1740</t>
+        </is>
+      </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2019-07-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2019-07-14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Noterad på lokal Störrestjärnen vid koordinat O1472960 N6946885 (±10m) RT90 2.5 gon. Kopia till Floraväkteriet.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2024,22 +2029,233 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Sven Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>80675790</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Rasktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>514209</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6944678</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2019-07-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2019-07-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Sven Bengtsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Sven Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>124123508</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bodtjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>513943</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6944755</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>Erik Söderhjelm</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>Erik Söderhjelm</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18634-2025 artfynd.xlsx
+++ b/artfynd/A 18634-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135538848</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135538849</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124123489</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124123530</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1191,6 +1216,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124123519</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1292,6 +1322,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124123540</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1393,6 +1428,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124123594</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1494,6 +1534,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124123602</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1600,6 +1645,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124123455</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1707,6 +1757,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80675791</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1822,6 +1877,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94564975</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1937,6 +1997,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94565032</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2046,6 +2111,11 @@
       <c r="AY14" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96561217</t>
         </is>
       </c>
     </row>
@@ -2155,6 +2225,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80675790</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2256,8 +2331,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124123508</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 18634-2025 artfynd.xlsx
+++ b/artfynd/A 18634-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135538848</v>
       </c>
       <c r="B2" t="n">
-        <v>97461</v>
+        <v>97505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>135538849</v>
       </c>
       <c r="B3" t="n">
-        <v>92369</v>
+        <v>92411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18634-2025 artfynd.xlsx
+++ b/artfynd/A 18634-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135538848</v>
       </c>
       <c r="B2" t="n">
-        <v>97505</v>
+        <v>97532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>135538849</v>
       </c>
       <c r="B3" t="n">
-        <v>92411</v>
+        <v>92438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18634-2025 artfynd.xlsx
+++ b/artfynd/A 18634-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124123489</v>
+        <v>135538848</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>97537</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrådmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cephalozia macounii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Austin) Austin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bodtjärn, Jmt</t>
+          <t>Barrskogen NV om Fisketjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514094</v>
+        <v>513946</v>
       </c>
       <c r="R2" t="n">
-        <v>6944657</v>
+        <v>6944708</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,27 +776,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erik Söderhjelm</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Söderhjelm</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124123489</t>
+          <t>https://artportalen.se/Sighting/135538848</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124123530</v>
+        <v>135538849</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>92443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,37 +804,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bodtjärn, Jmt</t>
+          <t>Barrskogen NV om Fisketjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513914</v>
+        <v>513946</v>
       </c>
       <c r="R3" t="n">
-        <v>6944835</v>
+        <v>6944708</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,19 +858,29 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
@@ -875,27 +889,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erik Söderhjelm</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erik Söderhjelm</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124123530</t>
+          <t>https://artportalen.se/Sighting/135538849</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124123519</v>
+        <v>124123489</v>
       </c>
       <c r="B4" t="n">
-        <v>80432</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +917,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513870</v>
+        <v>514094</v>
       </c>
       <c r="R4" t="n">
-        <v>6944774</v>
+        <v>6944657</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,38 +1006,38 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124123519</t>
+          <t>https://artportalen.se/Sighting/124123489</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124123540</v>
+        <v>124123530</v>
       </c>
       <c r="B5" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514085</v>
+        <v>513914</v>
       </c>
       <c r="R5" t="n">
-        <v>6944814</v>
+        <v>6944835</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,13 +1112,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124123540</t>
+          <t>https://artportalen.se/Sighting/124123530</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124123594</v>
+        <v>124123519</v>
       </c>
       <c r="B6" t="n">
         <v>80432</v>
@@ -1142,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514171</v>
+        <v>513870</v>
       </c>
       <c r="R6" t="n">
-        <v>6944779</v>
+        <v>6944774</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,13 +1218,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124123594</t>
+          <t>https://artportalen.se/Sighting/124123519</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124123602</v>
+        <v>124123540</v>
       </c>
       <c r="B7" t="n">
         <v>80432</v>
@@ -1248,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514264</v>
+        <v>514085</v>
       </c>
       <c r="R7" t="n">
-        <v>6944666</v>
+        <v>6944814</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,16 +1324,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124123602</t>
+          <t>https://artportalen.se/Sighting/124123540</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124123455</v>
+        <v>124123594</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,27 +1341,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1355,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514092</v>
+        <v>514171</v>
       </c>
       <c r="R8" t="n">
-        <v>6944610</v>
+        <v>6944779</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,17 +1406,13 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack i tall</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1421,55 +1430,54 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124123455</t>
+          <t>https://artportalen.se/Sighting/124123594</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>80675791</v>
+        <v>124123602</v>
       </c>
       <c r="B9" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>514260, Jmt</t>
+          <t>Bodtjärn, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514260</v>
+        <v>514264</v>
       </c>
       <c r="R9" t="n">
-        <v>6944655</v>
+        <v>6944666</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,12 +1504,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2019-07-14</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2019-07-14</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1514,82 +1522,69 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Erik Söderhjelm</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Erik Söderhjelm</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80675791</t>
+          <t>https://artportalen.se/Sighting/124123602</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>94564975</v>
+        <v>124123455</v>
       </c>
       <c r="B10" t="n">
-        <v>99118</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bodtjärn, dellokal 1, Jmt</t>
+          <t>Bodtjärn, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514269</v>
+        <v>514092</v>
       </c>
       <c r="R10" t="n">
-        <v>6944706</v>
+        <v>6944610</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,17 +1611,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Inga stänglar.</t>
+          <t>Ringhack i tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1635,31 +1630,30 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lars Grönvik</t>
+          <t>Erik Söderhjelm</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars Grönvik</t>
+          <t>Erik Söderhjelm</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94564975</t>
+          <t>https://artportalen.se/Sighting/124123455</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>94565032</v>
+        <v>80675791</v>
       </c>
       <c r="B11" t="n">
         <v>99118</v>
@@ -1687,29 +1681,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bodtjärn, dellokal 2, Jmt</t>
+          <t>514260, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514267</v>
+        <v>514260</v>
       </c>
       <c r="R11" t="n">
-        <v>6944688</v>
+        <v>6944655</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,17 +1722,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
+          <t>2019-07-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>En stängel på väg att utvecklas.</t>
+          <t>2019-07-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,27 +1740,32 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars Grönvik</t>
+          <t>Sven Bengtsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars Grönvik</t>
+          <t>Sven Bengtsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94565032</t>
+          <t>https://artportalen.se/Sighting/80675791</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96561217</v>
+        <v>94564975</v>
       </c>
       <c r="B12" t="n">
         <v>99118</v>
@@ -1807,20 +1793,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bodtjärnen /100 m S/, Jmt</t>
+          <t>Bodtjärn, dellokal 1, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514265</v>
+        <v>514269</v>
       </c>
       <c r="R12" t="n">
-        <v>6944683</v>
+        <v>6944706</v>
       </c>
       <c r="S12" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1842,24 +1840,19 @@
           <t>Bräcke</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>Z-Brä-1740</t>
-        </is>
-      </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2019-07-14</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2019-07-14</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Noterad på lokal Störrestjärnen vid koordinat O1472960 N6946885 (±10m) RT90 2.5 gon. Kopia till Floraväkteriet.</t>
+          <t>Inga stänglar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1868,76 +1861,81 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Lars Grönvik</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Lars Grönvik</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96561217</t>
+          <t>https://artportalen.se/Sighting/94564975</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>80675790</v>
+        <v>94565032</v>
       </c>
       <c r="B13" t="n">
-        <v>97989</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rasktjärnen, Jmt</t>
+          <t>Bodtjärn, dellokal 2, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514209</v>
+        <v>514267</v>
       </c>
       <c r="R13" t="n">
-        <v>6944678</v>
+        <v>6944688</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1964,12 +1962,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2019-07-14</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2019-07-14</t>
+          <t>2021-06-29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>En stängel på väg att utvecklas.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1982,76 +1985,68 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Lars Grönvik</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Lars Grönvik</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80675790</t>
+          <t>https://artportalen.se/Sighting/94565032</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124123508</v>
+        <v>96561217</v>
       </c>
       <c r="B14" t="n">
-        <v>80392</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bodtjärn, Jmt</t>
+          <t>Bodtjärnen /100 m S/, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513943</v>
+        <v>514265</v>
       </c>
       <c r="R14" t="n">
-        <v>6944755</v>
+        <v>6944683</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2073,14 +2068,24 @@
           <t>Bräcke</t>
         </is>
       </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Z-Brä-1740</t>
+        </is>
+      </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2019-07-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2019-07-14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Noterad på lokal Störrestjärnen vid koordinat O1472960 N6946885 (±10m) RT90 2.5 gon. Kopia till Floraväkteriet.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2089,23 +2094,244 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Sven Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96561217</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>80675790</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Rasktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>514209</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6944678</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2019-07-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2019-07-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Sven Bengtsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Sven Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80675790</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>124123508</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bodtjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>513943</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6944755</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>Erik Söderhjelm</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>Erik Söderhjelm</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr">
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/124123508</t>
         </is>
@@ -2126,6 +2352,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18634-2025 artfynd.xlsx
+++ b/artfynd/A 18634-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135538848</v>
       </c>
       <c r="B2" t="n">
-        <v>97537</v>
+        <v>97539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>135538849</v>
       </c>
       <c r="B3" t="n">
-        <v>92443</v>
+        <v>92445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18634-2025 artfynd.xlsx
+++ b/artfynd/A 18634-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135538848</v>
       </c>
       <c r="B2" t="n">
-        <v>97539</v>
+        <v>97556</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>135538849</v>
       </c>
       <c r="B3" t="n">
-        <v>92445</v>
+        <v>92459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18634-2025 artfynd.xlsx
+++ b/artfynd/A 18634-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135538848</v>
       </c>
       <c r="B2" t="n">
-        <v>97556</v>
+        <v>97557</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>135538849</v>
       </c>
       <c r="B3" t="n">
-        <v>92459</v>
+        <v>92460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
